--- a/artfynd/A 34621-2026 artfynd.xlsx
+++ b/artfynd/A 34621-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136192425</v>
       </c>
       <c r="B2" t="n">
-        <v>96618</v>
+        <v>96619</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136191414</v>
       </c>
       <c r="B5" t="n">
-        <v>96608</v>
+        <v>96609</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1141,7 +1141,7 @@
         <v>136192184</v>
       </c>
       <c r="B6" t="n">
-        <v>96597</v>
+        <v>96598</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         <v>136191740</v>
       </c>
       <c r="B7" t="n">
-        <v>96402</v>
+        <v>96403</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1365,7 +1365,7 @@
         <v>136192452</v>
       </c>
       <c r="B8" t="n">
-        <v>96402</v>
+        <v>96403</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 34621-2026 artfynd.xlsx
+++ b/artfynd/A 34621-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136192425</v>
       </c>
       <c r="B2" t="n">
-        <v>96619</v>
+        <v>96620</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136192041</v>
       </c>
       <c r="B3" t="n">
-        <v>77839</v>
+        <v>77840</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136192274</v>
       </c>
       <c r="B4" t="n">
-        <v>77839</v>
+        <v>77840</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136191414</v>
       </c>
       <c r="B5" t="n">
-        <v>96609</v>
+        <v>96610</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1141,7 +1141,7 @@
         <v>136192184</v>
       </c>
       <c r="B6" t="n">
-        <v>96598</v>
+        <v>96599</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         <v>136191740</v>
       </c>
       <c r="B7" t="n">
-        <v>96403</v>
+        <v>96404</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1365,7 +1365,7 @@
         <v>136192452</v>
       </c>
       <c r="B8" t="n">
-        <v>96403</v>
+        <v>96404</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1477,7 +1477,7 @@
         <v>136192201</v>
       </c>
       <c r="B9" t="n">
-        <v>83414</v>
+        <v>83415</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
         <v>136191497</v>
       </c>
       <c r="B10" t="n">
-        <v>79700</v>
+        <v>79701</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1701,7 +1701,7 @@
         <v>136191869</v>
       </c>
       <c r="B11" t="n">
-        <v>81107</v>
+        <v>81108</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 34621-2026 artfynd.xlsx
+++ b/artfynd/A 34621-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136192425</v>
       </c>
       <c r="B2" t="n">
-        <v>96620</v>
+        <v>96626</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136192041</v>
       </c>
       <c r="B3" t="n">
-        <v>77840</v>
+        <v>77844</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136192274</v>
       </c>
       <c r="B4" t="n">
-        <v>77840</v>
+        <v>77844</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136191414</v>
       </c>
       <c r="B5" t="n">
-        <v>96610</v>
+        <v>96616</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1141,7 +1141,7 @@
         <v>136192184</v>
       </c>
       <c r="B6" t="n">
-        <v>96599</v>
+        <v>96605</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         <v>136191740</v>
       </c>
       <c r="B7" t="n">
-        <v>96404</v>
+        <v>96410</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1365,7 +1365,7 @@
         <v>136192452</v>
       </c>
       <c r="B8" t="n">
-        <v>96404</v>
+        <v>96410</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1477,7 +1477,7 @@
         <v>136192201</v>
       </c>
       <c r="B9" t="n">
-        <v>83415</v>
+        <v>83419</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
         <v>136191497</v>
       </c>
       <c r="B10" t="n">
-        <v>79701</v>
+        <v>79705</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1701,7 +1701,7 @@
         <v>136191869</v>
       </c>
       <c r="B11" t="n">
-        <v>81108</v>
+        <v>81112</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 34621-2026 artfynd.xlsx
+++ b/artfynd/A 34621-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136192425</v>
       </c>
       <c r="B2" t="n">
-        <v>96626</v>
+        <v>96627</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136192041</v>
       </c>
       <c r="B3" t="n">
-        <v>77844</v>
+        <v>77845</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136192274</v>
       </c>
       <c r="B4" t="n">
-        <v>77844</v>
+        <v>77845</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136191414</v>
       </c>
       <c r="B5" t="n">
-        <v>96616</v>
+        <v>96617</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1141,7 +1141,7 @@
         <v>136192184</v>
       </c>
       <c r="B6" t="n">
-        <v>96605</v>
+        <v>96606</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         <v>136191740</v>
       </c>
       <c r="B7" t="n">
-        <v>96410</v>
+        <v>96411</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1365,7 +1365,7 @@
         <v>136192452</v>
       </c>
       <c r="B8" t="n">
-        <v>96410</v>
+        <v>96411</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1477,7 +1477,7 @@
         <v>136192201</v>
       </c>
       <c r="B9" t="n">
-        <v>83419</v>
+        <v>83420</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
         <v>136191497</v>
       </c>
       <c r="B10" t="n">
-        <v>79705</v>
+        <v>79706</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1701,7 +1701,7 @@
         <v>136191869</v>
       </c>
       <c r="B11" t="n">
-        <v>81112</v>
+        <v>81113</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 34621-2026 artfynd.xlsx
+++ b/artfynd/A 34621-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136192425</v>
       </c>
       <c r="B2" t="n">
-        <v>96627</v>
+        <v>96638</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136192041</v>
       </c>
       <c r="B3" t="n">
-        <v>77845</v>
+        <v>77849</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136192274</v>
       </c>
       <c r="B4" t="n">
-        <v>77845</v>
+        <v>77849</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136191414</v>
       </c>
       <c r="B5" t="n">
-        <v>96617</v>
+        <v>96628</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1141,7 +1141,7 @@
         <v>136192184</v>
       </c>
       <c r="B6" t="n">
-        <v>96606</v>
+        <v>96617</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         <v>136191740</v>
       </c>
       <c r="B7" t="n">
-        <v>96411</v>
+        <v>96422</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1365,7 +1365,7 @@
         <v>136192452</v>
       </c>
       <c r="B8" t="n">
-        <v>96411</v>
+        <v>96422</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1477,7 +1477,7 @@
         <v>136192201</v>
       </c>
       <c r="B9" t="n">
-        <v>83420</v>
+        <v>83424</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
         <v>136191497</v>
       </c>
       <c r="B10" t="n">
-        <v>79706</v>
+        <v>79710</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1701,7 +1701,7 @@
         <v>136191869</v>
       </c>
       <c r="B11" t="n">
-        <v>81113</v>
+        <v>81117</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 34621-2026 artfynd.xlsx
+++ b/artfynd/A 34621-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136192425</v>
       </c>
       <c r="B2" t="n">
-        <v>96638</v>
+        <v>96651</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136192041</v>
       </c>
       <c r="B3" t="n">
-        <v>77849</v>
+        <v>77855</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136192274</v>
       </c>
       <c r="B4" t="n">
-        <v>77849</v>
+        <v>77855</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136191414</v>
       </c>
       <c r="B5" t="n">
-        <v>96628</v>
+        <v>96641</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1141,7 +1141,7 @@
         <v>136192184</v>
       </c>
       <c r="B6" t="n">
-        <v>96617</v>
+        <v>96630</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         <v>136191740</v>
       </c>
       <c r="B7" t="n">
-        <v>96422</v>
+        <v>96435</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1365,7 +1365,7 @@
         <v>136192452</v>
       </c>
       <c r="B8" t="n">
-        <v>96422</v>
+        <v>96435</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1477,7 +1477,7 @@
         <v>136192201</v>
       </c>
       <c r="B9" t="n">
-        <v>83424</v>
+        <v>83430</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
         <v>136191497</v>
       </c>
       <c r="B10" t="n">
-        <v>79710</v>
+        <v>79716</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1701,7 +1701,7 @@
         <v>136191869</v>
       </c>
       <c r="B11" t="n">
-        <v>81117</v>
+        <v>81123</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 34621-2026 artfynd.xlsx
+++ b/artfynd/A 34621-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136192425</v>
       </c>
       <c r="B2" t="n">
-        <v>96651</v>
+        <v>96652</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136191414</v>
       </c>
       <c r="B5" t="n">
-        <v>96641</v>
+        <v>96642</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1141,7 +1141,7 @@
         <v>136192184</v>
       </c>
       <c r="B6" t="n">
-        <v>96630</v>
+        <v>96631</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         <v>136191740</v>
       </c>
       <c r="B7" t="n">
-        <v>96435</v>
+        <v>96436</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1365,7 +1365,7 @@
         <v>136192452</v>
       </c>
       <c r="B8" t="n">
-        <v>96435</v>
+        <v>96436</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 34621-2026 artfynd.xlsx
+++ b/artfynd/A 34621-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136192425</v>
       </c>
       <c r="B2" t="n">
-        <v>96652</v>
+        <v>96665</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136192041</v>
       </c>
       <c r="B3" t="n">
-        <v>77855</v>
+        <v>77868</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136192274</v>
       </c>
       <c r="B4" t="n">
-        <v>77855</v>
+        <v>77868</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136191414</v>
       </c>
       <c r="B5" t="n">
-        <v>96642</v>
+        <v>96655</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1141,7 +1141,7 @@
         <v>136192184</v>
       </c>
       <c r="B6" t="n">
-        <v>96631</v>
+        <v>96644</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         <v>136191740</v>
       </c>
       <c r="B7" t="n">
-        <v>96436</v>
+        <v>96449</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1365,7 +1365,7 @@
         <v>136192452</v>
       </c>
       <c r="B8" t="n">
-        <v>96436</v>
+        <v>96449</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1477,7 +1477,7 @@
         <v>136192201</v>
       </c>
       <c r="B9" t="n">
-        <v>83430</v>
+        <v>83443</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
         <v>136191497</v>
       </c>
       <c r="B10" t="n">
-        <v>79716</v>
+        <v>79729</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1701,7 +1701,7 @@
         <v>136191869</v>
       </c>
       <c r="B11" t="n">
-        <v>81123</v>
+        <v>81136</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 34621-2026 artfynd.xlsx
+++ b/artfynd/A 34621-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136192425</v>
       </c>
       <c r="B2" t="n">
-        <v>96665</v>
+        <v>96666</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136192041</v>
       </c>
       <c r="B3" t="n">
-        <v>77868</v>
+        <v>77869</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136192274</v>
       </c>
       <c r="B4" t="n">
-        <v>77868</v>
+        <v>77869</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136191414</v>
       </c>
       <c r="B5" t="n">
-        <v>96655</v>
+        <v>96656</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1141,7 +1141,7 @@
         <v>136192184</v>
       </c>
       <c r="B6" t="n">
-        <v>96644</v>
+        <v>96645</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         <v>136191740</v>
       </c>
       <c r="B7" t="n">
-        <v>96449</v>
+        <v>96450</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1365,7 +1365,7 @@
         <v>136192452</v>
       </c>
       <c r="B8" t="n">
-        <v>96449</v>
+        <v>96450</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1477,7 +1477,7 @@
         <v>136192201</v>
       </c>
       <c r="B9" t="n">
-        <v>83443</v>
+        <v>83444</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
         <v>136191497</v>
       </c>
       <c r="B10" t="n">
-        <v>79729</v>
+        <v>79730</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1701,7 +1701,7 @@
         <v>136191869</v>
       </c>
       <c r="B11" t="n">
-        <v>81136</v>
+        <v>81137</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
